--- a/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-26).xlsx
+++ b/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-26).xlsx
@@ -935,34 +935,34 @@
     <t>214</t>
   </si>
   <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>R$ 9.551,54</t>
-  </si>
-  <si>
-    <t>97.8</t>
-  </si>
-  <si>
-    <t>61.7</t>
-  </si>
-  <si>
-    <t>6.78</t>
-  </si>
-  <si>
-    <t>20.9</t>
-  </si>
-  <si>
-    <t>7.3</t>
-  </si>
-  <si>
-    <t>5.9</t>
-  </si>
-  <si>
-    <t>34.5%</t>
-  </si>
-  <si>
-    <t>16.3%</t>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 9.545,83</t>
+  </si>
+  <si>
+    <t>97.3</t>
+  </si>
+  <si>
+    <t>61.6</t>
+  </si>
+  <si>
+    <t>6.82</t>
+  </si>
+  <si>
+    <t>21.2</t>
+  </si>
+  <si>
+    <t>7.4</t>
+  </si>
+  <si>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>33.9%</t>
+  </si>
+  <si>
+    <t>16.2%</t>
   </si>
   <si>
     <t>1.3%</t>
@@ -980,25 +980,25 @@
     <t>0.3%</t>
   </si>
   <si>
-    <t>5.8%</t>
+    <t>5.7%</t>
   </si>
   <si>
     <t>4.9%</t>
   </si>
   <si>
-    <t>2084.0</t>
-  </si>
-  <si>
-    <t>1769.0</t>
-  </si>
-  <si>
-    <t>146.0</t>
-  </si>
-  <si>
-    <t>62.0</t>
-  </si>
-  <si>
-    <t>293.0</t>
+    <t>2107.0</t>
+  </si>
+  <si>
+    <t>1791.0</t>
+  </si>
+  <si>
+    <t>149.0</t>
+  </si>
+  <si>
+    <t>63.0</t>
+  </si>
+  <si>
+    <t>296.0</t>
   </si>
   <si>
     <t>102.0</t>
@@ -1007,16 +1007,16 @@
     <t>29.0</t>
   </si>
   <si>
-    <t>625.0</t>
-  </si>
-  <si>
-    <t>295.0</t>
-  </si>
-  <si>
-    <t>531.0</t>
-  </si>
-  <si>
-    <t>63.0</t>
+    <t>627.0</t>
+  </si>
+  <si>
+    <t>297.0</t>
+  </si>
+  <si>
+    <t>543.0</t>
+  </si>
+  <si>
+    <t>64.0</t>
   </si>
   <si>
     <t>1</t>
@@ -3272,7 +3272,9 @@
       <c r="N13" s="6">
         <v>135</v>
       </c>
-      <c r="O13" s="6"/>
+      <c r="O13" s="6">
+        <v>89</v>
+      </c>
       <c r="P13" s="7">
         <v>8.5050127819548873</v>
       </c>
@@ -3282,31 +3284,75 @@
       <c r="R13" s="8">
         <v>10.398863636363636</v>
       </c>
-      <c r="S13" s="8"/>
+      <c r="S13" s="8">
+        <v>7</v>
+      </c>
       <c r="T13" s="9">
         <v>0.06741573033707865</v>
       </c>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
-      <c r="AA13" s="9"/>
-      <c r="AB13" s="9"/>
-      <c r="AC13" s="9"/>
-      <c r="AD13" s="6"/>
-      <c r="AE13" s="6"/>
-      <c r="AF13" s="6"/>
-      <c r="AG13" s="6"/>
-      <c r="AH13" s="6"/>
-      <c r="AI13" s="6"/>
-      <c r="AJ13" s="6"/>
-      <c r="AK13" s="6"/>
-      <c r="AL13" s="6"/>
-      <c r="AM13" s="6"/>
-      <c r="AN13" s="9"/>
-      <c r="AO13" s="6"/>
+      <c r="U13" s="9">
+        <v>0.1797752808988764</v>
+      </c>
+      <c r="V13" s="9">
+        <v>0.02247191011235955</v>
+      </c>
+      <c r="W13" s="9">
+        <v>0</v>
+      </c>
+      <c r="X13" s="9">
+        <v>0.011235955056179775</v>
+      </c>
+      <c r="Y13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="9">
+        <v>0.011235955056179775</v>
+      </c>
+      <c r="AB13" s="9">
+        <v>0.011235955056179775</v>
+      </c>
+      <c r="AC13" s="9">
+        <v>0.11235955056179775</v>
+      </c>
+      <c r="AD13" s="6">
+        <v>16</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>16</v>
+      </c>
+      <c r="AF13" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL13" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM13" s="6">
+        <v>10</v>
+      </c>
+      <c r="AN13" s="9">
+        <v>0.011235955056179775</v>
+      </c>
+      <c r="AO13" s="6">
+        <v>1</v>
+      </c>
       <c t="s" r="AP13" s="4">
         <v>58</v>
       </c>
@@ -4909,7 +4955,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>51</v>
@@ -4939,14 +4985,26 @@
         <v>58</v>
       </c>
       <c r="L24" s="4"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="6"/>
+      <c r="M24" s="5">
+        <v>11175.92</v>
+      </c>
+      <c r="N24" s="6">
+        <v>125</v>
+      </c>
       <c r="O24" s="6"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
+      <c r="P24" s="7">
+        <v>7.7436636363636362</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>25.497569791666667</v>
+      </c>
+      <c r="R24" s="8">
+        <v>10.771701041666667</v>
+      </c>
       <c r="S24" s="8"/>
-      <c r="T24" s="9"/>
+      <c r="T24" s="9">
+        <v>0.041666666666666664</v>
+      </c>
       <c r="U24" s="9"/>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -9254,7 +9312,9 @@
       <c r="N53" s="6">
         <v>76</v>
       </c>
-      <c r="O53" s="6"/>
+      <c r="O53" s="6">
+        <v>44</v>
+      </c>
       <c r="P53" s="7">
         <v>3.5037276315789474</v>
       </c>
@@ -9264,31 +9324,75 @@
       <c r="R53" s="8">
         <v>4.6651522727272727</v>
       </c>
-      <c r="S53" s="8"/>
+      <c r="S53" s="8">
+        <v>7</v>
+      </c>
       <c r="T53" s="9">
         <v>0.63636363636363635</v>
       </c>
-      <c r="U53" s="9"/>
-      <c r="V53" s="9"/>
-      <c r="W53" s="9"/>
-      <c r="X53" s="9"/>
-      <c r="Y53" s="9"/>
-      <c r="Z53" s="9"/>
-      <c r="AA53" s="9"/>
-      <c r="AB53" s="9"/>
-      <c r="AC53" s="9"/>
-      <c r="AD53" s="6"/>
-      <c r="AE53" s="6"/>
-      <c r="AF53" s="6"/>
-      <c r="AG53" s="6"/>
-      <c r="AH53" s="6"/>
-      <c r="AI53" s="6"/>
-      <c r="AJ53" s="6"/>
-      <c r="AK53" s="6"/>
-      <c r="AL53" s="6"/>
-      <c r="AM53" s="6"/>
-      <c r="AN53" s="9"/>
-      <c r="AO53" s="6"/>
+      <c r="U53" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="V53" s="9">
+        <v>0.022727272727272728</v>
+      </c>
+      <c r="W53" s="9">
+        <v>0</v>
+      </c>
+      <c r="X53" s="9">
+        <v>0.022727272727272728</v>
+      </c>
+      <c r="Y53" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="9">
+        <v>0.045454545454545456</v>
+      </c>
+      <c r="AD53" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE53" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF53" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP53" s="4">
         <v>58</v>
       </c>
@@ -10016,7 +10120,7 @@
         <v>0.030612244897959183</v>
       </c>
       <c r="W58" s="9">
-        <v>0</v>
+        <v>0.010204081631999999</v>
       </c>
       <c r="X58" s="9">
         <v>0.01020408163265306</v>
@@ -10046,7 +10150,7 @@
         <v>3</v>
       </c>
       <c r="AG58" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH58" s="6">
         <v>1</v>
@@ -10736,7 +10840,7 @@
         <v>19632</v>
       </c>
       <c r="B63" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C63" s="4">
         <v>51</v>
@@ -10766,8 +10870,12 @@
         <v>58</v>
       </c>
       <c r="L63" s="4"/>
-      <c r="M63" s="5"/>
-      <c r="N63" s="6"/>
+      <c r="M63" s="5">
+        <v>0</v>
+      </c>
+      <c r="N63" s="6">
+        <v>0</v>
+      </c>
       <c r="O63" s="6"/>
       <c r="P63" s="7"/>
       <c r="Q63" s="8"/>
@@ -12589,7 +12697,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>51</v>
@@ -12617,35 +12725,93 @@
         <v>58</v>
       </c>
       <c r="L76" s="4"/>
-      <c r="M76" s="5"/>
-      <c r="N76" s="6"/>
-      <c r="O76" s="6"/>
-      <c r="P76" s="7"/>
-      <c r="Q76" s="8"/>
-      <c r="R76" s="8"/>
-      <c r="S76" s="8"/>
-      <c r="T76" s="9"/>
-      <c r="U76" s="9"/>
-      <c r="V76" s="9"/>
-      <c r="W76" s="9"/>
-      <c r="X76" s="9"/>
-      <c r="Y76" s="9"/>
-      <c r="Z76" s="9"/>
-      <c r="AA76" s="9"/>
-      <c r="AB76" s="9"/>
-      <c r="AC76" s="9"/>
-      <c r="AD76" s="6"/>
-      <c r="AE76" s="6"/>
-      <c r="AF76" s="6"/>
-      <c r="AG76" s="6"/>
-      <c r="AH76" s="6"/>
-      <c r="AI76" s="6"/>
-      <c r="AJ76" s="6"/>
-      <c r="AK76" s="6"/>
-      <c r="AL76" s="6"/>
-      <c r="AM76" s="6"/>
-      <c r="AN76" s="9"/>
-      <c r="AO76" s="6"/>
+      <c r="M76" s="5">
+        <v>11076.360000000001</v>
+      </c>
+      <c r="N76" s="6">
+        <v>123</v>
+      </c>
+      <c r="O76" s="6">
+        <v>72</v>
+      </c>
+      <c r="P76" s="7">
+        <v>6.5527559055118116</v>
+      </c>
+      <c r="Q76" s="8">
+        <v>41.696065277777777</v>
+      </c>
+      <c r="R76" s="8">
+        <v>26.282176388888889</v>
+      </c>
+      <c r="S76" s="8">
+        <v>9</v>
+      </c>
+      <c r="T76" s="9">
+        <v>0.027777777777777776</v>
+      </c>
+      <c r="U76" s="9">
+        <v>0.027777777777777776</v>
+      </c>
+      <c r="V76" s="9">
+        <v>0</v>
+      </c>
+      <c r="W76" s="9">
+        <v>0</v>
+      </c>
+      <c r="X76" s="9">
+        <v>0.013888888888888888</v>
+      </c>
+      <c r="Y76" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="9">
+        <v>0.013888888888888888</v>
+      </c>
+      <c r="AB76" s="9">
+        <v>0.013888888888888888</v>
+      </c>
+      <c r="AC76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD76" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK76" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL76" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO76" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP76" s="4">
         <v>58</v>
       </c>
@@ -14504,7 +14670,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14532,14 +14698,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>11174.9</v>
+      </c>
+      <c r="N89" s="6">
+        <v>102</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>13.918300980392157</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>34.191176470588232</v>
+      </c>
+      <c r="R89" s="8">
+        <v>11.387907843137256</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
@@ -31946,7 +32124,7 @@
         <v>19962</v>
       </c>
       <c r="B207" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C207" s="4">
         <v>51</v>
@@ -31976,35 +32154,93 @@
         <v>58</v>
       </c>
       <c r="L207" s="4"/>
-      <c r="M207" s="5"/>
-      <c r="N207" s="6"/>
-      <c r="O207" s="6"/>
-      <c r="P207" s="7"/>
-      <c r="Q207" s="8"/>
-      <c r="R207" s="8"/>
-      <c r="S207" s="8"/>
-      <c r="T207" s="9"/>
-      <c r="U207" s="9"/>
-      <c r="V207" s="9"/>
-      <c r="W207" s="9"/>
-      <c r="X207" s="9"/>
-      <c r="Y207" s="9"/>
-      <c r="Z207" s="9"/>
-      <c r="AA207" s="9"/>
-      <c r="AB207" s="9"/>
-      <c r="AC207" s="9"/>
-      <c r="AD207" s="6"/>
-      <c r="AE207" s="6"/>
-      <c r="AF207" s="6"/>
-      <c r="AG207" s="6"/>
-      <c r="AH207" s="6"/>
-      <c r="AI207" s="6"/>
-      <c r="AJ207" s="6"/>
-      <c r="AK207" s="6"/>
-      <c r="AL207" s="6"/>
-      <c r="AM207" s="6"/>
-      <c r="AN207" s="9"/>
-      <c r="AO207" s="6"/>
+      <c r="M207" s="5">
+        <v>3740.5900000000001</v>
+      </c>
+      <c r="N207" s="6">
+        <v>40</v>
+      </c>
+      <c r="O207" s="6">
+        <v>19</v>
+      </c>
+      <c r="P207" s="7">
+        <v>7.4258763157894734</v>
+      </c>
+      <c r="Q207" s="8">
+        <v>21.077194736842106</v>
+      </c>
+      <c r="R207" s="8">
+        <v>7.4447368421052627</v>
+      </c>
+      <c r="S207" s="8">
+        <v>7</v>
+      </c>
+      <c r="T207" s="9">
+        <v>0.10526315789473684</v>
+      </c>
+      <c r="U207" s="9">
+        <v>0</v>
+      </c>
+      <c r="V207" s="9">
+        <v>0</v>
+      </c>
+      <c r="W207" s="9">
+        <v>0</v>
+      </c>
+      <c r="X207" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y207" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM207" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN207" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO207" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP207" s="4">
         <v>58</v>
       </c>
